--- a/extenbooks/XS008_extenbook.xlsx
+++ b/extenbooks/XS008_extenbook.xlsx
@@ -708,7 +708,7 @@
         <v>1936</v>
       </c>
       <c r="B15" t="n">
-        <v>1.048547359126013</v>
+        <v>1.048547359126014</v>
       </c>
     </row>
     <row r="16">
@@ -764,7 +764,7 @@
         <v>1943</v>
       </c>
       <c r="B22" t="n">
-        <v>1.046993923887764</v>
+        <v>1.046993923887763</v>
       </c>
     </row>
     <row r="23">
@@ -1094,7 +1094,7 @@
         <v>1936</v>
       </c>
       <c r="B43" t="n">
-        <v>1.048547359126013</v>
+        <v>1.048547359126014</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1943</v>
       </c>
       <c r="B50" t="n">
-        <v>1.046993923887764</v>
+        <v>1.046993923887763</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GPIM Variant - Interwar Adjustment Multiplier</t>
+          <t>Generalized Perpetual Inventory Method (GPIM) variant, the interwar adjustment multiplier.</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: Appendix Table 6.8.II.5 column 'Adj. Ratio'. Intrinsically 1925-1947 only — feeds XS007/XS004 historical correction. No extension by construction. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source: Shaikh (2016), Appendix Table 6.8.II.5, column 'Adj. Ratio'. Intrinsically 1925-1947 only — it feeds the XS007/XS004 historical correction. No extension by construction.</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The `-A` suffix labels the single sub-variant of this series. The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau Historical Statistics 1975 (IRS book values), and the Federal Reserve Board G.17 release. All public domain.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Book period: 1925-1947. Vintage-stable extension recipe in `XS008_EPR.md`.</t>
+          <t>Book period: 1925-1947. See the companion Extension Provenance Record for details.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>`V03_XS008_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The series round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Two construction dependencies are resolved: the remapping of the NIPA Table 7.11 financial services indirectly measured (FISIM) lines, and the BEA 1993 depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS008 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Following the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline and the project's anti-degradation rule, **extension does NOT splice the published XS008 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>For XS008, the Phase 5 round-trip validation reads `XS008_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-1947. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS008, the round-trip validation reads the raw values from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-1947. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Proxy Use</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+          <t>No proxies are used in the book period; it is fully sourced from primary BEA / IRS / Census data.</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Synthetic Values</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the reconstructed BEA 1993 staged inputs).</t>
         </is>
       </c>
     </row>
@@ -1764,35 +1764,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | Loading fails with an explicit error |</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | Zero rows are recorded for that subseries and validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The re-fetch logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of the book period |</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| NIPA Table 7.11 financial services indirectly measured (FISIM) line revision (affecting XS003) | The line resolver falls back to the nearest pinned vintage with a logged warning | Re-mapped by label; vintage logged |</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation-rate inputs at 2011-vintage projection | Documented with the reconstructed BEA 1993 Fixed Asset methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Divergence From an Earlier Replication</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>Round-trip parity with an earlier replication is expected within tolerance for the book period. The comparison against the earlier replication's per-series output is informational when available.</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension Integrity</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension must re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end; splicing the published series is not permitted. Fetched BEA / FRED responses are cached with a 30-day time-to-live (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:50:53.093765+00:00</t>
+          <t>2026-07-02T06:28:51.602447+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS008_extenbook.xlsx
+++ b/extenbooks/XS008_extenbook.xlsx
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:28:51.602447+00:00</t>
+          <t>2026-07-11T03:44:27.604924+00:00</t>
         </is>
       </c>
     </row>
@@ -2112,11 +2112,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2139,6 +2139,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Single dimensionless multiplier (IRS index / BEA historical-cost index, 1925 = 1.0) that drives the 1925-1947 interwar correction feeding XS004/XS007. Renders sensibly as one trace; intrinsically a historical-correction series with no extension. Appendix Table 6.8.II.5 column 'Adj. Ratio'. Units already correctly per-series (dimensionless), no fix needed.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS008_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS008_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Source: Appendix Table 6.8.II.5 column 'Adj. Ratio'. Intrinsically 1925-1947 only — feeds XS007/XS004 historical correction. No extension by construction. | P2.6 F-P2.1-05: display corrected - XS008-A is the IRS book-value net-capital index alone (1925=1.0, 1947=1.202), NOT an IRS/BEA quotient (which would be ~0.79). It serves AS the interwar adjustment multiplier; the earlier 'IRS / BEA historical-cost index' phrasing misread the '/' as division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dimensionless_ratio_1925eq1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
